--- a/stories/arbres/ATOM-REL.MOQ.003-05.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Idriss rentre du square avec papa. Le soir, le salon est calme. Idriss a les joues chaudes. Il pense à des rires. Des enfants ont ri. Idriss a ri un peu aussi. Son ventre est serré. Maman s'assoit près de lui. Papa s'assoit aussi. Papa dit : tu peux raconter. Raconter, c'est dire ce qui s'est passé. Idriss dit : on a ri. J'ai ri aussi. Papa écoute. Maman dit : même si on a ri, on raconte. Même si on a ri, papa est là. Idriss raconte encore un peu. Il parle des rires. Il ne répète pas les mots. Plus tard, Idriss dit encore une chose. Même leçon, autre moment. Papa dit : merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Idriss boit de l'eau. Il se sent plus léger.</t>
+          <t>Idriss rentre du square avec papa. Le soir, le salon est calme. Idriss a les joues chaudes. Il pense à des rires. Des enfants ont ri. Idriss a ri un peu aussi. Son ventre est serré. Maman s'assoit près de lui. Papa s'assoit aussi. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. On a ri. J'ai ri aussi. Papa écoute. Même si on a ri, on raconte. Même si on a ri, papa est là. Idriss raconte encore un peu. Il parle des rires. Il ne répète pas les mots. Plus tard, Idriss dit encore une chose. Même leçon, autre moment. Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Idriss boit de l'eau. Il se sent plus léger.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Idriss rentre du square avec papa. Le soir, le salon est calme. Idriss a les joues chaudes. Il pense à des rires. Des enfants ont ri. Idriss a ri un peu aussi. Son ventre est serré. Maman s'assoit près de lui. Papa s'assoit aussi.
+papa|Tu peux raconter. Raconter, c'est dire ce qui s'est passé.
+enfant-m|On a ri. J'ai ri aussi. Papa écoute.
+maman|Même si on a ri, on raconte. Même si on a ri, papa est là.
+narrateur|Idriss raconte encore un peu. Il parle des rires. Il ne répète pas les mots. Plus tard, Idriss dit encore une chose. Même leçon, autre moment.
+papa|Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman.
+narrateur|Idriss boit de l'eau. Il se sent plus léger.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Idriss a ri un peu. Que fait-il le soir ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Idriss a su raconter. Même si on a ri, il a parlé à papa et maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Idriss met son pyjama. Papa lui tient la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.003-05.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Idriss boit de l'eau. Il se sent plus léger.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Idriss a ri un peu. Que fait-il le soir ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Idriss a su raconter. Même si on a ri, il a parlé à papa et maman.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Idriss met son pyjama. Papa lui tient la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.MOQ.003-05.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Idriss raconte, même s'il a ri</t>
+          <t>La fenêtre embuée de Raphaël</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La fenêtre du salon s'embue. Raphaël rentre du square. Même s'il a ri un peu, il raconte à papa et maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Idriss rentre du square avec papa. Le soir, le salon est calme. Idriss a les joues chaudes. Il pense à des rires. Des enfants ont ri. Idriss a ri un peu aussi. Son ventre est serré. Maman s'assoit près de lui. Papa s'assoit aussi. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. On a ri. J'ai ri aussi. Papa écoute. Même si on a ri, on raconte. Même si on a ri, papa est là. Idriss raconte encore un peu. Il parle des rires. Il ne répète pas les mots. Plus tard, Idriss dit encore une chose. Même leçon, autre moment. Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Idriss boit de l'eau. Il se sent plus léger.</t>
+          <t>La fenêtre du salon est un peu embuée. Le lampadaire de la rue fait une tache orange. Les chaussettes de laine sèchent sur le radiateur. Elles sentent le chaud, tout doux. La pendule du salon fait un tic lent. Un plaid gris attend sur le canapé. Le tissu du plaid est un peu rêche, un peu chaud. Une goutte glisse sur la vitre, tout lentement. Tes chaussettes vont être tièdes, Raphaël. Le square est fini, maintenant. On rentre. En ce moment, Raphaël rentre du square avec papa. Le salon est calme. Ses joues sont chaudes. Il pense à des rires, là-bas. Au square, il y a eu des rires. Raphaël a ri un peu aussi. Son ventre est serré. Papa. Maman. Mon ventre est serré. Je m'assois près de toi. Moi aussi. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. On a ri. J'ai ri aussi. Papa écoute. Maman écoute. Raphaël parle des rires. Il ne répète pas les mots. Même si on a ri, on raconte. Même si on a ri, papa t'écoute. Maman t'écoute aussi. C'était au square. Ça a duré un peu. Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Bravo, Raphaël. C'est du bon travail. Tu veux tes chaussettes chaudes ? Oui, maman. Les chaussettes sont tièdes sous ses pieds. Plus tard, Raphaël raconte encore une chose. J'ai pensé encore aux rires. Je vous le dis. Tu racontes encore. C'est bien. On t'écoute, à un autre moment aussi. Raphaël boit de l'eau. Il se sent plus léger. La tache orange du lampadaire reste sur la vitre. On met le plaid ? Oui. Près de vous. Tu as raconté. Même si tu as ri. Oui, maman. Le plaid couvre ses genoux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1324,65 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Idriss rentre du square avec papa. Le soir, le salon est calme. Idriss a les joues chaudes. Il pense à des rires. Des enfants ont ri. Idriss a ri un peu aussi. Son ventre est serré. Maman s'assoit près de lui. Papa s'assoit aussi.
-papa|Tu peux raconter. Raconter, c'est dire ce qui s'est passé.
-enfant-m|On a ri. J'ai ri aussi. Papa écoute.
-maman|Même si on a ri, on raconte. Même si on a ri, papa est là.
-narrateur|Idriss raconte encore un peu. Il parle des rires. Il ne répète pas les mots. Plus tard, Idriss dit encore une chose. Même leçon, autre moment.
-papa|Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman.
-narrateur|Idriss boit de l'eau. Il se sent plus léger.</t>
+          <t>narrateur|La fenêtre du salon est un peu embuée.
+narrateur|Le lampadaire de la rue fait une tache orange.
+narrateur|Les chaussettes de laine sèchent sur le radiateur.
+narrateur|Elles sentent le chaud, tout doux.
+narrateur|La pendule du salon fait un tic lent.
+narrateur|Un plaid gris attend sur le canapé.
+narrateur|Le tissu du plaid est un peu rêche, un peu chaud.
+narrateur|Une goutte glisse sur la vitre, tout lentement.
+maman|Tes chaussettes vont être tièdes, Raphaël.
+papa|Le square est fini, maintenant.
+papa|On rentre.
+narrateur|En ce moment, Raphaël rentre du square avec papa.
+narrateur|Le salon est calme.
+narrateur|Ses joues sont chaudes.
+narrateur|Il pense à des rires, là-bas.
+narrateur|Au square, il y a eu des rires.
+narrateur|Raphaël a ri un peu aussi.
+narrateur|Son ventre est serré.
+enfant-m|Papa.
+enfant-m|Maman.
+enfant-m|Mon ventre est serré.
+maman|Je m'assois près de toi.
+papa|Moi aussi.
+papa|Tu peux raconter.
+papa|Raconter, c'est dire ce qui s'est passé.
+enfant-m|On a ri.
+enfant-m|J'ai ri aussi.
+narrateur|Papa écoute.
+narrateur|Maman écoute.
+narrateur|Raphaël parle des rires.
+narrateur|Il ne répète pas les mots.
+maman|Même si on a ri, on raconte.
+maman|Même si on a ri, papa t'écoute.
+papa|Maman t'écoute aussi.
+enfant-m|C'était au square.
+enfant-m|Ça a duré un peu.
+papa|Merci d'avoir raconté.
+maman|Même si on a ri, on raconte à papa ou maman.
+papa|Bravo, Raphaël.
+papa|C'est du bon travail.
+maman|Tu veux tes chaussettes chaudes ?
+enfant-m|Oui, maman.
+narrateur|Les chaussettes sont tièdes sous ses pieds.
+narrateur|Plus tard, Raphaël raconte encore une chose.
+enfant-m|J'ai pensé encore aux rires.
+enfant-m|Je vous le dis.
+papa|Tu racontes encore.
+papa|C'est bien.
+maman|On t'écoute, à un autre moment aussi.
+narrateur|Raphaël boit de l'eau.
+narrateur|Il se sent plus léger.
+narrateur|La tache orange du lampadaire reste sur la vitre.
+papa|On met le plaid ?
+enfant-m|Oui.
+enfant-m|Près de vous.
+maman|Tu as raconté.
+maman|Même si tu as ri.
+enfant-m|Oui, maman.
+narrateur|Le plaid couvre ses genoux.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1346,7 +1410,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Idriss a ri un peu. Que fait-il le soir ?</t>
+          <t>Raphaël a ri un peu. Que fait-il le soir ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1566,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Idriss a ri un peu. Que fait-il le soir ?</t>
+          <t>narrateur|Raphaël a ri un peu.
+narrateur|Que fait-il le soir ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1595,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Idriss a su raconter. Même si on a ri, il a parlé à papa et maman.</t>
+          <t>Raphaël a su raconter. Même si on a ri, il a parlé à papa et maman. Tu es venu nous le dire. Bravo. C'est du bon travail, Raphaël. J'ai raconté. Même si j'ai ri. Oui. On raconte à papa ou maman. Le plaid est chaud sur ses genoux. La fenêtre s'embue encore un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1739,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Idriss a su raconter. Même si on a ri, il a parlé à papa et maman.</t>
+          <t>narrateur|Raphaël a su raconter.
+narrateur|Même si on a ri, il a parlé à papa et maman.
+papa|Tu es venu nous le dire.
+papa|Bravo.
+maman|C'est du bon travail, Raphaël.
+enfant-m|J'ai raconté.
+enfant-m|Même si j'ai ri.
+maman|Oui.
+maman|On raconte à papa ou maman.
+narrateur|Le plaid est chaud sur ses genoux.
+narrateur|La fenêtre s'embue encore un peu.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1777,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Idriss met son pyjama. Papa lui tient la main.</t>
+          <t>Raphaël met son pyjama. Le tissu sent le savon doux. Donne-moi ta main. Papa lui tient la main. Tes chaussettes sont au chaud, maintenant. On reste encore un peu ? Oui, papa. Près du canapé. La pendule fait encore tic. Le salon est calme. Le lampadaire brille tout loin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1917,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Idriss met son pyjama. Papa lui tient la main.</t>
+          <t>narrateur|Raphaël met son pyjama.
+narrateur|Le tissu sent le savon doux.
+papa|Donne-moi ta main.
+narrateur|Papa lui tient la main.
+maman|Tes chaussettes sont au chaud, maintenant.
+papa|On reste encore un peu ?
+enfant-m|Oui, papa.
+enfant-m|Près du canapé.
+maman|La pendule fait encore tic.
+narrateur|Le salon est calme.
+narrateur|Le lampadaire brille tout loin.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1955,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai raconté. Même si j'ai ri. Bravo. Tu as fait du bon travail. On t'a écouté. La fenêtre est encore un peu embuée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2095,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai raconté.
+enfant-m|Même si j'ai ri.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+narrateur|La fenêtre est encore un peu embuée.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.003-05.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La fenêtre du salon est un peu embuée. Le lampadaire de la rue fait une tache orange. Les chaussettes de laine sèchent sur le radiateur. Elles sentent le chaud, tout doux. La pendule du salon fait un tic lent. Un plaid gris attend sur le canapé. Le tissu du plaid est un peu rêche, un peu chaud. Une goutte glisse sur la vitre, tout lentement. Tes chaussettes vont être tièdes, Raphaël. Le square est fini, maintenant. On rentre. En ce moment, Raphaël rentre du square avec papa. Le salon est calme. Ses joues sont chaudes. Il pense à des rires, là-bas. Au square, il y a eu des rires. Raphaël a ri un peu aussi. Son ventre est serré. Papa. Maman. Mon ventre est serré. Je m'assois près de toi. Moi aussi. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. On a ri. J'ai ri aussi. Papa écoute. Maman écoute. Raphaël parle des rires. Il ne répète pas les mots. Même si on a ri, on raconte. Même si on a ri, papa t'écoute. Maman t'écoute aussi. C'était au square. Ça a duré un peu. Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Bravo, Raphaël. C'est du bon travail. Tu veux tes chaussettes chaudes ? Oui, maman. Les chaussettes sont tièdes sous ses pieds. Plus tard, Raphaël raconte encore une chose. J'ai pensé encore aux rires. Je vous le dis. Tu racontes encore. C'est bien. On t'écoute, à un autre moment aussi. Raphaël boit de l'eau. Il se sent plus léger. La tache orange du lampadaire reste sur la vitre. On met le plaid ? Oui. Près de vous. Tu as raconté. Même si tu as ri. Oui, maman. Le plaid couvre ses genoux.</t>
+          <t>La fenêtre du salon est un peu embuée. Le lampadaire de la rue fait une tache orange. Les chaussettes de laine sèchent sur le radiateur. Elles sentent le chaud, tout doux. La pendule du salon fait un tic lent. Un plaid gris attend sur le canapé. Le tissu du plaid est un peu rêche, un peu chaud. Une goutte glisse sur la vitre, tout lentement. Tes chaussettes vont être tièdes, Raphaël. Le square est fini, maintenant. On rentre. En ce moment, Raphaël rentre du square avec papa. Le salon est calme. Ses joues sont chaudes. Il pense à des rires, là-bas. Au square, il y a eu des rires. Raphaël a ri un peu aussi. Son ventre est serré. Papa. Maman. Mon ventre est serré. Je m'assois près de toi. Moi aussi. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. On a ri. J'ai ri aussi. Papa écoute. Maman écoute. Raphaël parle des rires. Il ne répète pas les mots. Même si on a ri, on raconte. Même si on a ri, papa t'écoute. Maman t'écoute aussi. C'était au square. Ça a duré un peu. Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Bravo, Raphaël. Tu veux tes chaussettes chaudes ? Oui, maman. Les chaussettes sont tièdes sous ses pieds. Plus tard, Raphaël raconte encore une chose. J'ai pensé encore aux rires. Je vous le dis. Tu racontes encore. C'est bien. On t'écoute, à un autre moment aussi. Raphaël boit de l'eau. Il se sent plus léger. La tache orange du lampadaire reste sur la vitre. On met le plaid ? Oui. Près de vous. Tu as raconté. Même si tu as ri. Oui, maman. Le plaid couvre ses genoux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Idriss rentre du square avec papa. Le soir, le salon est calme. Idriss a les joues chaudes. Il pense à des rires. Des enfants ont ri. Idriss a ri un peu aussi. Son ventre est serré. Maman s'assoit près de lui. Papa s'assoit aussi. Papa dit : tu peux &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt;. Raconter, c'est dire ce qui s'est passé. Idriss dit : on a ri. J'ai ri aussi. Papa écoute. Maman dit : même si on a ri, on raconte. Même si on a ri, papa est là. Idriss raconte encore un peu. Il parle des rires. Il ne répète pas les mots. Plus tard, Idriss dit encore une chose. Même leçon, autre moment. Papa dit : merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Idriss boit de l'eau. Il se sent plus léger.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La fenêtre du salon est un peu embuée. Le lampadaire de la rue fait une tache orange. Les chaussettes de laine sèchent sur le radiateur. Elles sentent le chaud, tout doux. La pendule du salon fait un tic lent. Un plaid gris attend sur le canapé. Le tissu du plaid est un peu rêche, un peu chaud. Une goutte glisse sur la vitre, tout lentement. Tes chaussettes vont être tièdes, Raphaël. Le square est fini, maintenant. On rentre. En ce moment, Raphaël rentre du square avec papa. Le salon est calme. Ses joues sont chaudes. Il pense à des rires, là-bas. Au square, il y a eu des rires. Raphaël a ri un peu aussi. Son ventre est serré. Papa. Maman. Mon ventre est serré. Je m'assois près de toi. Moi aussi. Tu peux raconter. Raconter, c'est dire ce qui s'est passé. On a ri. J'ai ri aussi. Papa écoute. Maman écoute. Raphaël parle des rires. Il ne répète pas les mots. Même si on a ri, on raconte. Même si on a ri, papa t'écoute. Maman t'écoute aussi. C'était au square. Ça a duré un peu. Merci d'avoir raconté. Même si on a ri, on raconte à papa ou maman. Bravo, Raphaël. Tu veux tes chaussettes chaudes ? Oui, maman. Les chaussettes sont tièdes sous ses pieds. Plus tard, Raphaël raconte encore une chose. J'ai pensé encore aux rires. Je vous le dis. Tu racontes encore. C'est bien. On t'écoute, à un autre moment aussi. Raphaël boit de l'eau. Il se sent plus léger. La tache orange du lampadaire reste sur la vitre. On met le plaid ? Oui. Près de vous. Tu as raconté. Même si tu as ri. Oui, maman. Le plaid couvre ses genoux.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1363,7 +1363,6 @@
 papa|Merci d'avoir raconté.
 maman|Même si on a ri, on raconte à papa ou maman.
 papa|Bravo, Raphaël.
-papa|C'est du bon travail.
 maman|Tu veux tes chaussettes chaudes ?
 enfant-m|Oui, maman.
 narrateur|Les chaussettes sont tièdes sous ses pieds.
@@ -1385,7 +1384,6 @@
 narrateur|Le plaid couvre ses genoux.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1415,7 +1413,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Idriss a ri un peu. Que fait-il le soir ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a ri un peu. Que fait-il le soir ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1570,7 +1568,6 @@
 narrateur|Que fait-il le soir ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1595,12 +1592,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a su raconter. Même si on a ri, il a parlé à papa et maman. Tu es venu nous le dire. Bravo. C'est du bon travail, Raphaël. J'ai raconté. Même si j'ai ri. Oui. On raconte à papa ou maman. Le plaid est chaud sur ses genoux. La fenêtre s'embue encore un peu.</t>
+          <t>Raphaël a su raconter. Même si on a ri, il a parlé à papa et maman. Tu es venu nous le dire. Bravo. J'ai raconté. Même si j'ai ri. Oui. On raconte à papa ou maman. Le plaid est chaud sur ses genoux. La fenêtre s'embue encore un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Idriss a su &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt;. Même si on a ri, il a parlé à papa et maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a su raconter. Même si on a ri, il a parlé à papa et maman. Tu es venu nous le dire. Bravo. J'ai raconté. Même si j'ai ri. Oui. On raconte à papa ou maman. Le plaid est chaud sur ses genoux. La fenêtre s'embue encore un peu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1743,7 +1740,6 @@
 narrateur|Même si on a ri, il a parlé à papa et maman.
 papa|Tu es venu nous le dire.
 papa|Bravo.
-maman|C'est du bon travail, Raphaël.
 enfant-m|J'ai raconté.
 enfant-m|Même si j'ai ri.
 maman|Oui.
@@ -1752,7 +1748,6 @@
 narrateur|La fenêtre s'embue encore un peu.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1782,7 +1777,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Idriss met son pyjama. Papa lui tient la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël met son pyjama. Le tissu sent le savon doux. Donne-moi ta main. Papa lui tient la main. Tes chaussettes sont au chaud, maintenant. On reste encore un peu ? Oui, papa. Près du canapé. La pendule fait encore tic. Le salon est calme. Le lampadaire brille tout loin.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1930,7 +1925,6 @@
 narrateur|Le lampadaire brille tout loin.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1955,12 +1949,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai raconté. Même si j'ai ri. Bravo. Tu as fait du bon travail. On t'a écouté. La fenêtre est encore un peu embuée. L'histoire est finie.</t>
+          <t>J'ai raconté. Même si j'ai ri. Bravo. On t'a écouté. La fenêtre est encore un peu embuée.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai raconté. Même si j'ai ri. Bravo. On t'a écouté. La fenêtre est encore un peu embuée.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2098,13 +2092,10 @@
           <t>enfant-m|J'ai raconté.
 enfant-m|Même si j'ai ri.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 maman|On t'a écouté.
-narrateur|La fenêtre est encore un peu embuée.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La fenêtre est encore un peu embuée.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2123,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2159,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.003-05.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.003-05.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Idriss, papa, maman</t>
+          <t>Raphaël, papa, maman</t>
         </is>
       </c>
     </row>
